--- a/payroll/2026/excel/20260924-0925.xlsx
+++ b/payroll/2026/excel/20260924-0925.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lubaoqiang\git\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C248A6F-AEDB-4C1A-8608-D1C713F71649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AFFAEC-5C46-43AF-9C2E-4058FFD615C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24890" windowHeight="14620" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="1350" yWindow="40" windowWidth="22600" windowHeight="13960" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="4" r:id="rId1"/>
@@ -443,7 +443,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
